--- a/Listing/PPT03D.xlsx
+++ b/Listing/PPT03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="267">
   <si>
     <t/>
   </si>
@@ -103,15 +103,27 @@
     <t>SOFTX GRVTY 23CM 28S</t>
   </si>
   <si>
-    <t>20133906</t>
-  </si>
-  <si>
-    <t>HER'S PRTX NAT WG22S</t>
+    <t>20141368</t>
+  </si>
+  <si>
+    <t>HERS CL.BRZ 17S-23.5</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20141367</t>
+  </si>
+  <si>
+    <t>HERS CL BRZE 12'S-30</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20120202</t>
   </si>
   <si>
@@ -160,9 +172,6 @@
     <t>SOFTEX PL DS NP 44'S</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20081895</t>
   </si>
   <si>
@@ -277,9 +286,6 @@
     <t>LAURIER SLM GRD DY16</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
     <t>20125494</t>
   </si>
   <si>
@@ -337,7 +343,7 @@
     <t>20094211</t>
   </si>
   <si>
-    <t>IDM SERBET SRBGN 26S</t>
+    <t>IDM SERBET SRBGN 25S</t>
   </si>
   <si>
     <t>20046211</t>
@@ -583,15 +589,21 @@
     <t>CHARM NIGHT WG 18/29</t>
   </si>
   <si>
+    <t>20140802</t>
+  </si>
+  <si>
+    <t>IDM TISU DAPUR 1+1</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>20115506</t>
   </si>
   <si>
     <t>IDM TISU BMB ROL 4'S</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>20140801</t>
   </si>
   <si>
@@ -607,199 +619,199 @@
     <t>16</t>
   </si>
   <si>
-    <t>20113001</t>
-  </si>
-  <si>
-    <t>IDM ALCHOL WIPE 10'S</t>
+    <t>20141206</t>
+  </si>
+  <si>
+    <t>LARISST M.W WIPE 8X8</t>
+  </si>
+  <si>
+    <t>20140679</t>
+  </si>
+  <si>
+    <t>IDM FC.TISSUE 3X80'S</t>
+  </si>
+  <si>
+    <t>20124826</t>
+  </si>
+  <si>
+    <t>FAVOUR TISU WJH 120S</t>
+  </si>
+  <si>
+    <t>20103297</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP200</t>
+  </si>
+  <si>
+    <t>20133704</t>
+  </si>
+  <si>
+    <t>IDM BB.FCL TISSU 70S</t>
+  </si>
+  <si>
+    <t>20141207</t>
+  </si>
+  <si>
+    <t>WATERU WHT BMBOO 50S</t>
+  </si>
+  <si>
+    <t>20098520</t>
+  </si>
+  <si>
+    <t>IDM TISSUE PNGST 150</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20045887</t>
+  </si>
+  <si>
+    <t>IDM TISU DP/HND 150S</t>
+  </si>
+  <si>
+    <t>10038692</t>
+  </si>
+  <si>
+    <t>MULTI TIS.NON.PERPUM</t>
+  </si>
+  <si>
+    <t>20122914</t>
+  </si>
+  <si>
+    <t>FAVOUR CH FC TIS200S</t>
+  </si>
+  <si>
+    <t>20020128</t>
+  </si>
+  <si>
+    <t>NICE FC/TISUE NP250S</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20026897</t>
+  </si>
+  <si>
+    <t>TESSA FAC.TISSUE 260</t>
+  </si>
+  <si>
+    <t>20034036</t>
+  </si>
+  <si>
+    <t>PASEO SMART 540PLY</t>
+  </si>
+  <si>
+    <t>10005468</t>
+  </si>
+  <si>
+    <t>PASEO FC.SOFT 510PLY</t>
+  </si>
+  <si>
+    <t>20139653</t>
+  </si>
+  <si>
+    <t>LRST FAC.TIS 2X200S</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20113083</t>
+  </si>
+  <si>
+    <t>TESSA FC.TISU 2X200S</t>
+  </si>
+  <si>
+    <t>10014168</t>
+  </si>
+  <si>
+    <t>NICE BUY1FREE1 2X200</t>
+  </si>
+  <si>
+    <t>20128974</t>
+  </si>
+  <si>
+    <t>MONTISS FC TISUE200S</t>
+  </si>
+  <si>
+    <t>20035998</t>
+  </si>
+  <si>
+    <t>INDOMRET TRVL PACK50</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20006422</t>
+  </si>
+  <si>
+    <t>TESSA FAC.LOONEY TP9</t>
+  </si>
+  <si>
+    <t>20001221</t>
+  </si>
+  <si>
+    <t>PASEO TRVL.PC TISSUE</t>
+  </si>
+  <si>
+    <t>20063288</t>
+  </si>
+  <si>
+    <t>PASEO PURE SOFT 130S</t>
+  </si>
+  <si>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20114021</t>
+  </si>
+  <si>
+    <t>IDM TISU WJH PRM 100</t>
+  </si>
+  <si>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
+  </si>
+  <si>
+    <t>20115171</t>
+  </si>
+  <si>
+    <t>IDM TISU BAMBU 150'S</t>
+  </si>
+  <si>
+    <t>20048847</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP900</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20098229</t>
-  </si>
-  <si>
-    <t>WATERU BMBO TISS 6'S</t>
-  </si>
-  <si>
-    <t>20140679</t>
-  </si>
-  <si>
-    <t>IDM FC.TISSUE 3X80'S</t>
-  </si>
-  <si>
-    <t>20124826</t>
-  </si>
-  <si>
-    <t>FAVOUR TISU WJH 120S</t>
-  </si>
-  <si>
-    <t>20103297</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP200</t>
-  </si>
-  <si>
-    <t>10038692</t>
-  </si>
-  <si>
-    <t>MULTI TIS.NON.PERPUM</t>
-  </si>
-  <si>
-    <t>20098520</t>
-  </si>
-  <si>
-    <t>IDM TISSUE PNGST 150</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20045887</t>
-  </si>
-  <si>
-    <t>IDM TISU DP/HND 150S</t>
-  </si>
-  <si>
-    <t>10005468</t>
-  </si>
-  <si>
-    <t>PASEO FC.SOFT 510PLY</t>
-  </si>
-  <si>
-    <t>20026897</t>
-  </si>
-  <si>
-    <t>TESSA FAC.TISSUE 260</t>
-  </si>
-  <si>
-    <t>20034036</t>
-  </si>
-  <si>
-    <t>PASEO SMART 540PLY</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20006422</t>
-  </si>
-  <si>
-    <t>TESSA FAC.LOONEY TP9</t>
-  </si>
-  <si>
-    <t>20001221</t>
-  </si>
-  <si>
-    <t>PASEO TRVL.PC TISSUE</t>
-  </si>
-  <si>
-    <t>20133704</t>
-  </si>
-  <si>
-    <t>IDM BB.FCL TISSU 70S</t>
-  </si>
-  <si>
-    <t>20122914</t>
-  </si>
-  <si>
-    <t>FAVOUR CH FC TIS200S</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20020128</t>
-  </si>
-  <si>
-    <t>NICE FC/TISUE NP250S</t>
-  </si>
-  <si>
-    <t>20113083</t>
-  </si>
-  <si>
-    <t>TESSA FC.TISU 2X200S</t>
-  </si>
-  <si>
-    <t>20128974</t>
-  </si>
-  <si>
-    <t>MONTISS FC TISUE200S</t>
-  </si>
-  <si>
-    <t>20131625</t>
-  </si>
-  <si>
-    <t>LARISST FCL.TIS 250S</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20035998</t>
-  </si>
-  <si>
-    <t>INDOMRET TRVL PACK50</t>
-  </si>
-  <si>
-    <t>20115171</t>
-  </si>
-  <si>
-    <t>IDM TISU BAMBU 150'S</t>
-  </si>
-  <si>
-    <t>10014168</t>
-  </si>
-  <si>
-    <t>NICE BUY1FREE1 2X200</t>
-  </si>
-  <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20114021</t>
-  </si>
-  <si>
-    <t>IDM TISU WJH PRM 100</t>
-  </si>
-  <si>
-    <t>20063288</t>
-  </si>
-  <si>
-    <t>PASEO PURE SOFT 130S</t>
-  </si>
-  <si>
-    <t>20048847</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP900</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
-  </si>
-  <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
-  </si>
-  <si>
-    <t>20139653</t>
-  </si>
-  <si>
-    <t>LRST FAC.TIS 2X200S</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1440,35 +1452,35 @@
         <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1477,7 +1489,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>12</v>
@@ -1485,10 +1497,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1497,18 +1509,18 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1517,18 +1529,18 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1537,18 +1549,18 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1557,18 +1569,18 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1577,7 +1589,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>12</v>
@@ -1585,10 +1597,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1597,7 +1609,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>12</v>
@@ -1614,10 +1626,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -1625,10 +1637,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1637,7 +1649,7 @@
         <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>12</v>
@@ -1645,10 +1657,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1657,7 +1669,7 @@
         <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>12</v>
@@ -1665,10 +1677,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1677,7 +1689,7 @@
         <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>12</v>
@@ -1685,10 +1697,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1697,38 +1709,38 @@
         <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1737,7 +1749,7 @@
         <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>12</v>
@@ -1745,10 +1757,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1757,10 +1769,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1777,18 +1789,18 @@
         <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1797,18 +1809,18 @@
         <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1817,38 +1829,38 @@
         <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1857,7 +1869,7 @@
         <v>32</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1865,10 +1877,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1877,18 +1889,18 @@
         <v>32</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1897,18 +1909,18 @@
         <v>32</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1917,7 +1929,7 @@
         <v>32</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>12</v>
@@ -1925,10 +1937,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1937,10 +1949,10 @@
         <v>32</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1954,13 +1966,13 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1974,13 +1986,13 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1994,13 +2006,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2014,10 +2026,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>12</v>
@@ -2034,13 +2046,13 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2054,10 +2066,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>19</v>
@@ -2074,13 +2086,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2094,10 +2106,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>12</v>
@@ -2114,13 +2126,13 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2134,13 +2146,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2154,33 +2166,33 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2194,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>19</v>
@@ -2214,10 +2226,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -2234,13 +2246,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2254,13 +2266,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2274,13 +2286,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2294,13 +2306,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2314,30 +2326,30 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2354,13 +2366,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2374,10 +2386,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>12</v>
@@ -2394,13 +2406,13 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2414,30 +2426,30 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>12</v>
@@ -2454,10 +2466,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>12</v>
@@ -2474,13 +2486,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2494,50 +2506,50 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2554,10 +2566,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2574,10 +2586,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2594,10 +2606,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2614,13 +2626,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2634,13 +2646,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2654,30 +2666,30 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="E74" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2694,10 +2706,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2714,10 +2726,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2734,10 +2746,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2754,13 +2766,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2774,10 +2786,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>12</v>
@@ -2785,19 +2797,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>12</v>
@@ -2814,10 +2826,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>12</v>
@@ -2834,10 +2846,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>12</v>
@@ -2854,13 +2866,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2874,13 +2886,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2894,30 +2906,30 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -2934,70 +2946,70 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>200</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>12</v>
@@ -3005,19 +3017,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>12</v>
@@ -3025,59 +3037,59 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3085,79 +3097,79 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>12</v>
@@ -3165,19 +3177,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>12</v>
@@ -3185,19 +3197,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>12</v>
@@ -3205,39 +3217,39 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>12</v>
@@ -3245,19 +3257,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>12</v>
@@ -3265,39 +3277,39 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>12</v>
@@ -3305,59 +3317,59 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3365,19 +3377,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>12</v>
@@ -3385,79 +3397,79 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3465,39 +3477,39 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3505,22 +3517,62 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
